--- a/Checklist - Artefato 1.xlsx
+++ b/Checklist - Artefato 1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rafael Fernandes\Downloads\ChecklistQualidade\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A538841\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8054943-FD90-494A-A447-990CDF007192}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6E509ECB-B77C-4447-8B3D-F96372A744D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4672E65F-BD16-49AF-B984-110D5D3DB6D8}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{4672E65F-BD16-49AF-B984-110D5D3DB6D8}"/>
   </bookViews>
   <sheets>
     <sheet name="Checklist" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="69">
   <si>
     <t xml:space="preserve">Resultado </t>
   </si>
@@ -165,6 +165,87 @@
   </si>
   <si>
     <t>Aderência</t>
+  </si>
+  <si>
+    <t>Conforme</t>
+  </si>
+  <si>
+    <t>Não Conforme</t>
+  </si>
+  <si>
+    <t>O campo "Nome do Produto" está preenchido corretamente com ELDERIA, logo abaixo do cabeçalho do quadro.</t>
+  </si>
+  <si>
+    <t>O quadro traz exatamente três objetivos numerados (1, 2 e 3), cada um com sua descrição.</t>
+  </si>
+  <si>
+    <t>Os três objetivos (facilitar acesso à saúde, dar autonomia ao idoso e dar visibilidade ao profissional) conversam diretamente com o problema descrito nos Artefatos 2 e 4.</t>
+  </si>
+  <si>
+    <t>Os objetivos atingem os dois públicos-alvo definidos no Artefato 3: idosos e profissionais da saúde e bem-estar.</t>
+  </si>
+  <si>
+    <t>Os três objetivos refletem as prioridades centrais do produto identificadas nos demais artefatos.</t>
+  </si>
+  <si>
+    <t>Nenhum dos objetivos entra em conflito com o "Não faz" do Artefato 2 (chamar ambulância, atender emergência, contratar profissional).</t>
+  </si>
+  <si>
+    <t>Os objetivos são amplos o bastante para continuarem fazendo sentido mesmo se o produto evoluir.</t>
+  </si>
+  <si>
+    <t>O cabeçalho do quadro está identificado como "ARTEFATO 1".</t>
+  </si>
+  <si>
+    <t>A redação de cada objetivo é curta e direta.</t>
+  </si>
+  <si>
+    <t>Os objetivos são compatíveis com as funcionalidades de busca, agendamento e divulgação de serviços descritas no Canvas PBB (Artefato 4).</t>
+  </si>
+  <si>
+    <t>Os objetivos estão de acordo com a finalidade apresentada nos Artefatos 2 e 3.</t>
+  </si>
+  <si>
+    <t>O objetivo 2 fala diretamente do benefício ao idoso: mais independência para marcar consultas.</t>
+  </si>
+  <si>
+    <t>O objetivo 1 menciona explicitamente "facilitar o acesso à saúde complementar".</t>
+  </si>
+  <si>
+    <t>Não identificamos ambiguidade na redação dos três objetivos.</t>
+  </si>
+  <si>
+    <t>Cada objetivo aborda um aspecto diferente (acesso, autonomia, visibilidade), sem repetir conteúdo.</t>
+  </si>
+  <si>
+    <t>Não encontramos erros que atrapalhem o entendimento dos objetivos.</t>
+  </si>
+  <si>
+    <t>Os objetivos são específicos o suficiente para servirem de referência ao avaliar se o produto cumpre sua proposta.</t>
+  </si>
+  <si>
+    <t>Cada objetivo tem uma finalidade própria e distinta.</t>
+  </si>
+  <si>
+    <t>O objetivo 3 cita explicitamente "profissionais da área de saúde e bem-estar" como beneficiários do produto.</t>
+  </si>
+  <si>
+    <t>Incluir um título ou identificação específica para cada objetivo, permitindo verificar claramente se sua descrição está diretamente relacionada ao respectivo objetivo</t>
+  </si>
+  <si>
+    <t>Menor</t>
+  </si>
+  <si>
+    <t>O quadro não tem um campo de "título" separado por objetivo, só número e descrição, então esse item não se aplica à forma como o artefato foi estruturado.</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Enviado</t>
+  </si>
+  <si>
+    <t>Matheus Fuchs</t>
   </si>
 </sst>
 </file>
@@ -284,7 +365,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -306,21 +387,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -331,6 +397,22 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -666,64 +748,64 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63381509-777B-4F7A-965D-F5E2BE998752}">
   <dimension ref="B2:I31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.33203125" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.77734375" style="3" customWidth="1"/>
-    <col min="4" max="4" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.5546875" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
-    <col min="7" max="7" width="26.6640625" customWidth="1"/>
-    <col min="8" max="8" width="25.109375" customWidth="1"/>
-    <col min="9" max="9" width="21.33203125" customWidth="1"/>
+    <col min="1" max="1" width="7.36328125" customWidth="1"/>
+    <col min="2" max="2" width="11.453125" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.81640625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="19.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.54296875" customWidth="1"/>
+    <col min="6" max="6" width="143.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26.6328125" customWidth="1"/>
+    <col min="8" max="8" width="141" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="C2" s="15" t="s">
+    <row r="2" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="C2" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="17"/>
-      <c r="F2" s="9" t="s">
+      <c r="D2" s="12"/>
+      <c r="F2" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.35">
       <c r="C3" s="8" t="s">
         <v>27</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="G3" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="I3" s="16" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:9" x14ac:dyDescent="0.35">
       <c r="C4" s="8" t="s">
         <v>29</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="12"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="13"/>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="F4" s="15"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="17"/>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.35">
       <c r="C5" s="8" t="s">
         <v>31</v>
       </c>
@@ -731,23 +813,23 @@
         <v>32</v>
       </c>
       <c r="F5" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="H5" s="1">
-        <v>0</v>
-      </c>
-      <c r="I5" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="I5" s="18">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.35">
       <c r="C6" s="8"/>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:9" x14ac:dyDescent="0.35">
       <c r="C7" s="8" t="s">
         <v>33</v>
       </c>
@@ -755,321 +837,561 @@
         <v>36</v>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.35">
       <c r="C8" s="8" t="s">
         <v>34</v>
       </c>
       <c r="D8" s="1"/>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.35">
       <c r="C9" s="8" t="s">
         <v>35</v>
       </c>
       <c r="D9" s="1"/>
     </row>
-    <row r="11" spans="2:9" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="14" t="s">
+    <row r="11" spans="2:9" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C11" s="15"/>
-      <c r="D11" s="16" t="s">
+      <c r="C11" s="10"/>
+      <c r="D11" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="E11" s="16" t="s">
+      <c r="E11" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="F11" s="16" t="s">
+      <c r="F11" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="G11" s="16" t="s">
+      <c r="G11" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="H11" s="16" t="s">
+      <c r="H11" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="I11" s="16" t="s">
+      <c r="I11" s="11" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="2:9" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:9" ht="28" x14ac:dyDescent="0.35">
       <c r="B12" s="5">
         <v>1</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D12" s="6"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-    </row>
-    <row r="13" spans="2:9" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="D12" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" ht="28" x14ac:dyDescent="0.35">
       <c r="B13" s="5">
         <v>2</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="6"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-    </row>
-    <row r="14" spans="2:9" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="D13" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" ht="28" x14ac:dyDescent="0.35">
       <c r="B14" s="5">
         <v>3</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="6"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-    </row>
-    <row r="15" spans="2:9" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="D14" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" ht="28" x14ac:dyDescent="0.35">
       <c r="B15" s="5">
         <v>4</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D15" s="6"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-    </row>
-    <row r="16" spans="2:9" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="D15" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" ht="28" x14ac:dyDescent="0.35">
       <c r="B16" s="5">
         <v>5</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D16" s="6"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-    </row>
-    <row r="17" spans="2:9" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="D16" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" ht="42" x14ac:dyDescent="0.35">
       <c r="B17" s="5">
         <v>6</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="6"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-    </row>
-    <row r="18" spans="2:9" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="D17" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" ht="28" x14ac:dyDescent="0.35">
       <c r="B18" s="5">
         <v>7</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="6"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-    </row>
-    <row r="19" spans="2:9" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="D18" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" ht="28" x14ac:dyDescent="0.35">
       <c r="B19" s="5">
         <v>8</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D19" s="6"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-    </row>
-    <row r="20" spans="2:9" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="D19" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" ht="28" x14ac:dyDescent="0.35">
       <c r="B20" s="5">
         <v>9</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="6"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-    </row>
-    <row r="21" spans="2:9" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="D20" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" ht="42" x14ac:dyDescent="0.35">
       <c r="B21" s="5">
         <v>10</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D21" s="6"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-    </row>
-    <row r="22" spans="2:9" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="D21" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" ht="42" x14ac:dyDescent="0.35">
       <c r="B22" s="5">
         <v>11</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="6"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-    </row>
-    <row r="23" spans="2:9" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="D22" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" ht="28" x14ac:dyDescent="0.35">
       <c r="B23" s="5">
         <v>12</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D23" s="6"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-    </row>
-    <row r="24" spans="2:9" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="D23" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" ht="42" x14ac:dyDescent="0.35">
       <c r="B24" s="5">
         <v>13</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D24" s="6"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-    </row>
-    <row r="25" spans="2:9" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="D24" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" ht="28" x14ac:dyDescent="0.35">
       <c r="B25" s="5">
         <v>14</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D25" s="6"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-    </row>
-    <row r="26" spans="2:9" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="D25" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" ht="28" x14ac:dyDescent="0.35">
       <c r="B26" s="5">
         <v>15</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D26" s="6"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-    </row>
-    <row r="27" spans="2:9" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="D26" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9" ht="42" x14ac:dyDescent="0.35">
       <c r="B27" s="5">
         <v>16</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D27" s="6"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-    </row>
-    <row r="28" spans="2:9" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="D27" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9" ht="42" x14ac:dyDescent="0.35">
       <c r="B28" s="5">
         <v>17</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D28" s="6"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-    </row>
-    <row r="29" spans="2:9" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="D28" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9" ht="42" x14ac:dyDescent="0.35">
       <c r="B29" s="5">
         <v>18</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D29" s="6"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
-    </row>
-    <row r="30" spans="2:9" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="D29" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9" ht="28" x14ac:dyDescent="0.35">
       <c r="B30" s="5">
         <v>19</v>
       </c>
       <c r="C30" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D30" s="6"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-    </row>
-    <row r="31" spans="2:9" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="D30" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9" ht="42" x14ac:dyDescent="0.35">
       <c r="B31" s="5">
         <v>20</v>
       </c>
       <c r="C31" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D31" s="6"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
+      <c r="D31" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>66</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1085,23 +1407,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="aed73f09-bf5d-4147-a3d9-eca4840d3416" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007CCF20922A0DE34DA3357EDA40AE3850" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="df2c289d3a08b18055ba2ef47a57998b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="aed73f09-bf5d-4147-a3d9-eca4840d3416" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="91dac5f1c2bd6141b57005fd2a16424c" ns3:_="">
     <xsd:import namespace="aed73f09-bf5d-4147-a3d9-eca4840d3416"/>
@@ -1251,7 +1556,42 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="aed73f09-bf5d-4147-a3d9-eca4840d3416" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4FC09F85-4182-458C-9936-A4A27B890011}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="aed73f09-bf5d-4147-a3d9-eca4840d3416"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD41F362-A534-43BD-873B-83E80A9078F7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -1267,7 +1607,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{901F3B13-F474-42C6-B910-1EF2E5DFC5CC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -1275,20 +1615,8 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4FC09F85-4182-458C-9936-A4A27B890011}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="aed73f09-bf5d-4147-a3d9-eca4840d3416"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{19540963-e559-4020-8a90-fe8a502c2801}" enabled="1" method="Standard" siteId="{f25493ae-1c98-41d7-8a33-0be75f5fe603}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>